--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A961373A-1035-44CF-9471-47800DAEEEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B47A6-66A2-4797-B07F-5CD1E6806346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,12 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1027,7 @@
         <v>49</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>51</v>
@@ -1031,26 +1037,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="8">
+        <v>46245</v>
+      </c>
+      <c r="B7" s="9">
+        <v>420</v>
+      </c>
+      <c r="C7" s="9">
+        <v>60</v>
+      </c>
+      <c r="D7" s="9">
+        <v>60</v>
+      </c>
+      <c r="E7" s="9">
+        <v>60</v>
+      </c>
+      <c r="F7" s="9">
+        <v>180</v>
+      </c>
+      <c r="G7" s="9">
+        <v>3</v>
+      </c>
+      <c r="H7" s="9">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="13"/>
